--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="D3">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -433,10 +433,10 @@
         <v>328</v>
       </c>
       <c r="D2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -453,10 +453,10 @@
         <v>382</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
